--- a/crates/xlstream-eval/tests/fixtures/operators/concatenation.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/operators/concatenation.xlsx
@@ -20,54 +20,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMEA</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_multi</t>
   </si>
   <si>
     <t xml:space="preserve">hello</t>
   </si>
   <si>
-    <t xml:space="preserve">APAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  spaces  here  </t>
+    <t xml:space="preserve">world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
   </si>
   <si>
     <t xml:space="preserve">abc</t>
   </si>
   <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProPer Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo bar</t>
+    <t xml:space="preserve">foo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
   </si>
 </sst>
 </file>
@@ -340,7 +352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -353,125 +365,200 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="0" t="str">
         <f aca="false">A2&amp;B2</f>
-        <v>EMEAhello</v>
+        <v>helloworld</v>
+      </c>
+      <c r="D2" s="0" t="str">
+        <f aca="false">A2&amp;"-"&amp;B2</f>
+        <v>hello-world</v>
+      </c>
+      <c r="E2" s="0" t="str">
+        <f aca="false">A2&amp;""</f>
+        <v>hello</v>
+      </c>
+      <c r="F2" s="0" t="str">
+        <f aca="false">A2&amp;" "&amp;B2&amp;"!"</f>
+        <v>hello world!</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
       <c r="B3" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="0" t="str">
         <f aca="false">A3&amp;B3</f>
-        <v>APACWORLD</v>
+        <v>test</v>
+      </c>
+      <c r="D3" s="0" t="str">
+        <f aca="false">A3&amp;"-"&amp;B3</f>
+        <v>-test</v>
+      </c>
+      <c r="E3" s="0" t="str">
+        <f aca="false">A3&amp;""</f>
+        <v/>
+      </c>
+      <c r="F3" s="0" t="str">
+        <f aca="false">A3&amp;" "&amp;B3&amp;"!"</f>
+        <v> test!</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="str">
         <f aca="false">A4&amp;B4</f>
-        <v>AMER  spaces  here  </v>
+        <v>abc</v>
+      </c>
+      <c r="D4" s="0" t="str">
+        <f aca="false">A4&amp;"-"&amp;B4</f>
+        <v>abc-</v>
+      </c>
+      <c r="E4" s="0" t="str">
+        <f aca="false">A4&amp;""</f>
+        <v>abc</v>
+      </c>
+      <c r="F4" s="0" t="str">
+        <f aca="false">A4&amp;" "&amp;B4&amp;"!"</f>
+        <v>abc !</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="0" t="str">
         <f aca="false">A5&amp;B5</f>
-        <v>EMEAabc</v>
+        <v>foobar</v>
+      </c>
+      <c r="D5" s="0" t="str">
+        <f aca="false">A5&amp;"-"&amp;B5</f>
+        <v>foo-bar</v>
+      </c>
+      <c r="E5" s="0" t="str">
+        <f aca="false">A5&amp;""</f>
+        <v>foo</v>
+      </c>
+      <c r="F5" s="0" t="str">
+        <f aca="false">A5&amp;" "&amp;B5&amp;"!"</f>
+        <v>foo bar!</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="0" t="str">
         <f aca="false">A6&amp;B6</f>
-        <v>APACshort</v>
+        <v>AB</v>
+      </c>
+      <c r="D6" s="0" t="str">
+        <f aca="false">A6&amp;"-"&amp;B6</f>
+        <v>A-B</v>
+      </c>
+      <c r="E6" s="0" t="str">
+        <f aca="false">A6&amp;""</f>
+        <v>A</v>
+      </c>
+      <c r="F6" s="0" t="str">
+        <f aca="false">A6&amp;" "&amp;B6&amp;"!"</f>
+        <v>A B!</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="0" t="str">
         <f aca="false">A7&amp;B7</f>
-        <v>AMERtest</v>
+        <v>123456</v>
+      </c>
+      <c r="D7" s="0" t="str">
+        <f aca="false">A7&amp;"-"&amp;B7</f>
+        <v>123-456</v>
+      </c>
+      <c r="E7" s="0" t="str">
+        <f aca="false">A7&amp;""</f>
+        <v>123</v>
+      </c>
+      <c r="F7" s="0" t="str">
+        <f aca="false">A7&amp;" "&amp;B7&amp;"!"</f>
+        <v>123 456!</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">A8&amp;B8</f>
-        <v>EMEAProPer Case</v>
+        <v>  x</v>
+      </c>
+      <c r="D8" s="0" t="str">
+        <f aca="false">A8&amp;"-"&amp;B8</f>
+        <v>  -x</v>
+      </c>
+      <c r="E8" s="0" t="str">
+        <f aca="false">A8&amp;""</f>
+        <v>  </v>
+      </c>
+      <c r="F8" s="0" t="str">
+        <f aca="false">A8&amp;" "&amp;B8&amp;"!"</f>
+        <v>   x!</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">A9&amp;B9</f>
-        <v>APACnum123</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="0" t="str">
-        <f aca="false">A10&amp;B10</f>
-        <v>AMERfoo bar</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="0" t="str">
-        <f aca="false">A11&amp;B11</f>
-        <v>EMEAx</v>
+        <v>longstring</v>
+      </c>
+      <c r="D9" s="0" t="str">
+        <f aca="false">A9&amp;"-"&amp;B9</f>
+        <v>long-string</v>
+      </c>
+      <c r="E9" s="0" t="str">
+        <f aca="false">A9&amp;""</f>
+        <v>long</v>
+      </c>
+      <c r="F9" s="0" t="str">
+        <f aca="false">A9&amp;" "&amp;B9&amp;"!"</f>
+        <v>long string!</v>
       </c>
     </row>
   </sheetData>
